--- a/data/trans_orig/Q4506_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q4506_R-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31197</t>
+          <t>30978</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56605</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66567</t>
+          <t>67430</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98461</t>
+          <t>98341</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104380</t>
+          <t>104762</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147674</t>
+          <t>145872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36328</t>
+          <t>38001</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65367</t>
+          <t>65651</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50740</t>
+          <t>49612</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81960</t>
+          <t>80964</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94656</t>
+          <t>95836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137483</t>
+          <t>139806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60580</t>
+          <t>60953</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93974</t>
+          <t>95184</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42452</t>
+          <t>42275</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70674</t>
+          <t>70994</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112079</t>
+          <t>110921</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>157576</t>
+          <t>155784</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55594</t>
+          <t>58356</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89549</t>
+          <t>89679</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19033</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39792</t>
+          <t>39014</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79139</t>
+          <t>81795</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118664</t>
+          <t>120662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174682</t>
+          <t>174173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>216882</t>
+          <t>218155</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66358</t>
+          <t>66162</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99809</t>
+          <t>99920</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>250028</t>
+          <t>250056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>307137</t>
+          <t>306729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29919</t>
+          <t>29131</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56626</t>
+          <t>58204</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55981</t>
+          <t>55411</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87656</t>
+          <t>88498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90876</t>
+          <t>92795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133938</t>
+          <t>136802</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42628</t>
+          <t>41979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72602</t>
+          <t>72910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47524</t>
+          <t>47166</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77136</t>
+          <t>77436</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97919</t>
+          <t>94342</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139745</t>
+          <t>137080</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66675</t>
+          <t>67095</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>101754</t>
+          <t>102709</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58370</t>
+          <t>59116</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90534</t>
+          <t>94496</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>135102</t>
+          <t>134097</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>180357</t>
+          <t>181134</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34581</t>
+          <t>36015</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62532</t>
+          <t>63533</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40364</t>
+          <t>40618</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58982</t>
+          <t>59055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93789</t>
+          <t>94980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167194</t>
+          <t>165738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211218</t>
+          <t>209632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88232</t>
+          <t>85025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123474</t>
+          <t>121875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>266032</t>
+          <t>264958</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>321820</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41839</t>
+          <t>41512</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72700</t>
+          <t>73343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43518</t>
+          <t>43462</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71641</t>
+          <t>72100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92141</t>
+          <t>94209</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134454</t>
+          <t>136688</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40929</t>
+          <t>40540</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68816</t>
+          <t>68220</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19969</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41147</t>
+          <t>41022</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66414</t>
+          <t>68188</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>102503</t>
+          <t>102564</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73948</t>
+          <t>74105</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>108540</t>
+          <t>112511</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34449</t>
+          <t>33422</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58991</t>
+          <t>58587</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>114987</t>
+          <t>115942</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>158247</t>
+          <t>161137</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68174</t>
+          <t>67296</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103153</t>
+          <t>102829</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13255</t>
+          <t>13087</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30542</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87276</t>
+          <t>85658</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127390</t>
+          <t>124462</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>315741</t>
+          <t>313914</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>367475</t>
+          <t>365198</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92826</t>
+          <t>92720</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>125673</t>
+          <t>124591</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>420567</t>
+          <t>418392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>478922</t>
+          <t>480955</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62913</t>
+          <t>61976</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99710</t>
+          <t>99001</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118874</t>
+          <t>119707</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>163884</t>
+          <t>162728</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>192202</t>
+          <t>190619</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>248942</t>
+          <t>248382</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74278</t>
+          <t>73890</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114939</t>
+          <t>111815</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103294</t>
+          <t>102683</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>146544</t>
+          <t>147100</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>189179</t>
+          <t>186300</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>246159</t>
+          <t>241056</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>145486</t>
+          <t>144024</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>195597</t>
+          <t>193888</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>109363</t>
+          <t>107531</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>152841</t>
+          <t>151605</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>266732</t>
+          <t>267691</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>329472</t>
+          <t>331396</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>104461</t>
+          <t>104165</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>147384</t>
+          <t>148653</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62709</t>
+          <t>64155</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96703</t>
+          <t>98090</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>176420</t>
+          <t>175605</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>233738</t>
+          <t>233650</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>659159</t>
+          <t>664450</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>729892</t>
+          <t>728939</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>267557</t>
+          <t>265647</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>322867</t>
+          <t>322421</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>946657</t>
+          <t>946196</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1036948</t>
+          <t>1035651</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16802</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>36459</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>138570</t>
+          <t>139844</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>185067</t>
+          <t>181961</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>160372</t>
+          <t>159017</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>211066</t>
+          <t>211289</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30927</t>
+          <t>32393</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>57470</t>
+          <t>56750</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>85009</t>
+          <t>84833</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>122231</t>
+          <t>123386</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>122989</t>
+          <t>122404</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>171191</t>
+          <t>168848</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>50832</t>
+          <t>52235</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>82328</t>
+          <t>83018</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>100757</t>
+          <t>102143</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>142043</t>
+          <t>141958</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>161853</t>
+          <t>160965</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>214268</t>
+          <t>213588</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>45625</t>
+          <t>45525</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>73131</t>
+          <t>74442</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32392</t>
+          <t>34444</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>61498</t>
+          <t>62436</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>86346</t>
+          <t>86507</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>127116</t>
+          <t>126030</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>293523</t>
+          <t>296164</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>338911</t>
+          <t>338892</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>302265</t>
+          <t>300657</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>357795</t>
+          <t>357068</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>611972</t>
+          <t>612759</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>684009</t>
+          <t>684028</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>37987</t>
+          <t>38181</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>172373</t>
+          <t>171158</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>222490</t>
+          <t>226937</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>193521</t>
+          <t>195743</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>248511</t>
+          <t>251919</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>15045</t>
+          <t>14289</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>33889</t>
+          <t>34986</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>118308</t>
+          <t>118019</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>162630</t>
+          <t>160967</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>140919</t>
+          <t>139215</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>189273</t>
+          <t>188686</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>21333</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>40744</t>
+          <t>41309</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>206000</t>
+          <t>203874</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>258862</t>
+          <t>257952</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>233117</t>
+          <t>231675</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>288579</t>
+          <t>289878</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>40302</t>
+          <t>41056</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>66840</t>
+          <t>67248</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>86551</t>
+          <t>87840</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>126813</t>
+          <t>126365</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>136943</t>
+          <t>137774</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>184444</t>
+          <t>184953</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>118988</t>
+          <t>118812</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>150939</t>
+          <t>151130</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>400909</t>
+          <t>402011</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>467052</t>
+          <t>470379</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>531675</t>
+          <t>531441</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>604503</t>
+          <t>603369</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,98%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>235320</t>
+          <t>236859</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>304097</t>
+          <t>301810</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>657454</t>
+          <t>665427</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>756026</t>
+          <t>763180</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>914784</t>
+          <t>914022</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1039068</t>
+          <t>1044444</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>286653</t>
+          <t>284933</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>358348</t>
+          <t>351716</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>475196</t>
+          <t>480342</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>565496</t>
+          <t>567785</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>782544</t>
+          <t>775101</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>899066</t>
+          <t>893852</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>472211</t>
+          <t>472016</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>564649</t>
+          <t>562142</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>609065</t>
+          <t>611662</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>701850</t>
+          <t>702792</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1106036</t>
+          <t>1113554</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1234541</t>
+          <t>1234857</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>398598</t>
+          <t>398654</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>481492</t>
+          <t>481484</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>276664</t>
+          <t>276435</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>344389</t>
+          <t>341355</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>697398</t>
+          <t>697008</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>804970</t>
+          <t>802770</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1814826</t>
+          <t>1813482</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1938973</t>
+          <t>1935805</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1290784</t>
+          <t>1296487</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1404178</t>
+          <t>1415319</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3142320</t>
+          <t>3142576</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3311839</t>
+          <t>3319121</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,71%</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54580</t>
+          <t>57241</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87626</t>
+          <t>88689</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92769</t>
+          <t>94162</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128716</t>
+          <t>129142</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>157291</t>
+          <t>156514</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>204923</t>
+          <t>204316</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94279</t>
+          <t>93322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130917</t>
+          <t>130222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92301</t>
+          <t>94684</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128408</t>
+          <t>129489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197643</t>
+          <t>198119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249813</t>
+          <t>249868</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61842</t>
+          <t>60877</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95025</t>
+          <t>95358</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48168</t>
+          <t>49235</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76329</t>
+          <t>77126</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118001</t>
+          <t>118423</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>161110</t>
+          <t>161976</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33951</t>
+          <t>35067</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60383</t>
+          <t>60135</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17263</t>
+          <t>17046</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36188</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57683</t>
+          <t>58498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89204</t>
+          <t>89227</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102359</t>
+          <t>104112</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142993</t>
+          <t>143494</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27174</t>
+          <t>25924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52697</t>
+          <t>51789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137532</t>
+          <t>136764</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184626</t>
+          <t>184309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40800</t>
+          <t>42733</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69463</t>
+          <t>70814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83007</t>
+          <t>82198</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117945</t>
+          <t>117568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133520</t>
+          <t>131849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178985</t>
+          <t>182370</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55819</t>
+          <t>55346</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86774</t>
+          <t>85304</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91598</t>
+          <t>89365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127204</t>
+          <t>126170</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156993</t>
+          <t>156645</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202447</t>
+          <t>202235</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51662</t>
+          <t>51223</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82210</t>
+          <t>83805</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51960</t>
+          <t>51964</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81197</t>
+          <t>81254</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>111095</t>
+          <t>112211</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>155089</t>
+          <t>155874</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>39401</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65289</t>
+          <t>65594</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18450</t>
+          <t>19807</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40145</t>
+          <t>41060</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63320</t>
+          <t>63973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96839</t>
+          <t>95612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113388</t>
+          <t>112893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151081</t>
+          <t>150533</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54642</t>
+          <t>54255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85473</t>
+          <t>85520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>176309</t>
+          <t>176507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>226384</t>
+          <t>225630</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>37367</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65016</t>
+          <t>65732</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>20707</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41446</t>
+          <t>42235</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63945</t>
+          <t>64393</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100730</t>
+          <t>98809</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88076</t>
+          <t>88399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>125679</t>
+          <t>124043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32582</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55781</t>
+          <t>55181</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>127334</t>
+          <t>129361</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171651</t>
+          <t>172769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66868</t>
+          <t>67706</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>101028</t>
+          <t>102881</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15155</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33216</t>
+          <t>32991</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>86466</t>
+          <t>88375</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>127351</t>
+          <t>126089</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42777</t>
+          <t>44079</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72197</t>
+          <t>71407</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21982</t>
+          <t>23314</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>55534</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88214</t>
+          <t>88902</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200962</t>
+          <t>200286</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245117</t>
+          <t>246166</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44353</t>
+          <t>43109</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69006</t>
+          <t>68524</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>251861</t>
+          <t>253079</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>308017</t>
+          <t>305398</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69806</t>
+          <t>68880</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105799</t>
+          <t>105684</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>153196</t>
+          <t>151729</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>200518</t>
+          <t>199927</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230777</t>
+          <t>231206</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>291661</t>
+          <t>289733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178924</t>
+          <t>178962</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>232349</t>
+          <t>230343</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>191436</t>
+          <t>192929</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>242447</t>
+          <t>243752</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>384661</t>
+          <t>382572</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>456560</t>
+          <t>456510</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>162149</t>
+          <t>160398</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>212256</t>
+          <t>211400</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126726</t>
+          <t>126728</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>171808</t>
+          <t>170679</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>300446</t>
+          <t>302323</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>370024</t>
+          <t>368642</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>131048</t>
+          <t>130968</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178568</t>
+          <t>177684</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63390</t>
+          <t>62657</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95378</t>
+          <t>95858</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>205577</t>
+          <t>203635</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>264878</t>
+          <t>264664</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>478501</t>
+          <t>481144</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>548945</t>
+          <t>548230</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>178750</t>
+          <t>175578</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>229334</t>
+          <t>224146</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8287,12 +8287,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>674081</t>
+          <t>675599</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>761225</t>
+          <t>760072</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28439</t>
+          <t>28892</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53322</t>
+          <t>54436</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>109363</t>
+          <t>109654</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>151626</t>
+          <t>148912</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>146530</t>
+          <t>146241</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>193766</t>
+          <t>192001</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8580,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>66629</t>
+          <t>66887</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>101768</t>
+          <t>101948</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129002</t>
+          <t>132340</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>175441</t>
+          <t>176401</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>210422</t>
+          <t>205833</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>267782</t>
+          <t>264693</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>54890</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>84707</t>
+          <t>87457</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>120548</t>
+          <t>117709</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>163468</t>
+          <t>160649</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>185687</t>
+          <t>184431</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>239544</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>43038</t>
+          <t>43074</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>71195</t>
+          <t>72721</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>49192</t>
+          <t>50210</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>81157</t>
+          <t>81376</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>98709</t>
+          <t>98748</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>142821</t>
+          <t>143292</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>345519</t>
+          <t>344331</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>394145</t>
+          <t>395485</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>225651</t>
+          <t>226790</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>277452</t>
+          <t>276127</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>588405</t>
+          <t>585347</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>664092</t>
+          <t>657104</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,43%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>44664</t>
+          <t>44308</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>168782</t>
+          <t>165124</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>220403</t>
+          <t>220029</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>198499</t>
+          <t>200053</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>257698</t>
+          <t>254051</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -9262,12 +9262,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>59261</t>
+          <t>59211</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>87869</t>
+          <t>88819</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9297,12 +9297,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>249971</t>
+          <t>251449</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>309140</t>
+          <t>308995</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9332,12 +9332,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>319670</t>
+          <t>317588</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>383052</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -9375,12 +9375,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>38498</t>
+          <t>38752</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>65010</t>
+          <t>66033</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9410,12 +9410,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>159899</t>
+          <t>160400</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>209149</t>
+          <t>212658</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>208358</t>
+          <t>208499</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>262987</t>
+          <t>265970</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -9488,12 +9488,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>24889</t>
+          <t>24896</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>47981</t>
+          <t>47485</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>60631</t>
+          <t>58082</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>94774</t>
+          <t>92830</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>91709</t>
+          <t>93005</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>132591</t>
+          <t>132903</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -9601,12 +9601,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>77199</t>
+          <t>77945</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>109533</t>
+          <t>108679</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9636,12 +9636,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>313215</t>
+          <t>313330</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>376219</t>
+          <t>378561</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>403215</t>
+          <t>404776</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>474473</t>
+          <t>470487</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -9831,12 +9831,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>301452</t>
+          <t>300926</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>372880</t>
+          <t>371789</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9846,12 +9846,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9866,12 +9866,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>694958</t>
+          <t>687292</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>795719</t>
+          <t>784824</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1008260</t>
+          <t>1008889</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1132993</t>
+          <t>1138492</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -9944,12 +9944,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>601170</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>694921</t>
+          <t>696258</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9959,12 +9959,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>861703</t>
+          <t>864947</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>966359</t>
+          <t>969984</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1489764</t>
+          <t>1491724</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1636588</t>
+          <t>1633060</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>488463</t>
+          <t>492310</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>574765</t>
+          <t>578191</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10072,12 +10072,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>581068</t>
+          <t>578426</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>672296</t>
+          <t>668481</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1087432</t>
+          <t>1096499</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1214035</t>
+          <t>1222439</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -10170,12 +10170,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>357548</t>
+          <t>360421</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>438223</t>
+          <t>438392</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>255744</t>
+          <t>252664</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>317655</t>
+          <t>317950</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>637787</t>
+          <t>630118</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>739196</t>
+          <t>737876</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -10283,12 +10283,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1400685</t>
+          <t>1400057</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1513521</t>
+          <t>1513282</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>911636</t>
+          <t>902875</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1018389</t>
+          <t>1015806</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2330241</t>
+          <t>2336547</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2493338</t>
+          <t>2501981</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4506_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q4506_R-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>30988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56638</t>
+          <t>55323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67430</t>
+          <t>68147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98341</t>
+          <t>100856</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104762</t>
+          <t>104258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145872</t>
+          <t>147615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38001</t>
+          <t>37100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65651</t>
+          <t>65144</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49612</t>
+          <t>50399</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80964</t>
+          <t>80992</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95836</t>
+          <t>97802</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139806</t>
+          <t>137859</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60953</t>
+          <t>61140</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95184</t>
+          <t>93942</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42275</t>
+          <t>42733</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70994</t>
+          <t>70056</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>110921</t>
+          <t>111673</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155784</t>
+          <t>156651</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58356</t>
+          <t>56320</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89679</t>
+          <t>89639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18266</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39014</t>
+          <t>38589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81795</t>
+          <t>82029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120662</t>
+          <t>119502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174173</t>
+          <t>173677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>218155</t>
+          <t>215763</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66162</t>
+          <t>66114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99920</t>
+          <t>98730</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>250056</t>
+          <t>247226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>306729</t>
+          <t>305971</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,81%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29131</t>
+          <t>28931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58204</t>
+          <t>55103</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55411</t>
+          <t>56953</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88498</t>
+          <t>88056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92795</t>
+          <t>91764</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136802</t>
+          <t>134583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41979</t>
+          <t>42160</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72910</t>
+          <t>73605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47166</t>
+          <t>47810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77436</t>
+          <t>77191</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>94342</t>
+          <t>97418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137080</t>
+          <t>138612</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67095</t>
+          <t>66740</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102709</t>
+          <t>101372</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59116</t>
+          <t>60675</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>94496</t>
+          <t>90111</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>134097</t>
+          <t>133895</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>181134</t>
+          <t>180852</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36015</t>
+          <t>35645</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63533</t>
+          <t>60532</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>19396</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40618</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59055</t>
+          <t>59000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94980</t>
+          <t>92924</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165738</t>
+          <t>168235</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>209632</t>
+          <t>211087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85025</t>
+          <t>85943</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>121875</t>
+          <t>123204</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>264958</t>
+          <t>264816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>321560</t>
+          <t>321382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41512</t>
+          <t>41283</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73343</t>
+          <t>71562</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43462</t>
+          <t>43338</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72100</t>
+          <t>72169</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94209</t>
+          <t>91755</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136688</t>
+          <t>132998</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40540</t>
+          <t>40915</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68220</t>
+          <t>68966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41022</t>
+          <t>41786</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68188</t>
+          <t>67437</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>102564</t>
+          <t>103445</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74105</t>
+          <t>74307</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>112511</t>
+          <t>110447</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33422</t>
+          <t>33167</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58587</t>
+          <t>59422</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>115942</t>
+          <t>116008</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>161137</t>
+          <t>158875</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67296</t>
+          <t>68704</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102829</t>
+          <t>103596</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13087</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>30848</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85658</t>
+          <t>85456</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>124462</t>
+          <t>124381</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>313914</t>
+          <t>315372</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>365198</t>
+          <t>366723</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92720</t>
+          <t>92415</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>124591</t>
+          <t>124182</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>418392</t>
+          <t>420099</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>480955</t>
+          <t>479019</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,03%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61976</t>
+          <t>60952</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99001</t>
+          <t>97867</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119707</t>
+          <t>121067</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>162728</t>
+          <t>164211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190619</t>
+          <t>190208</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>248382</t>
+          <t>249329</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>73890</t>
+          <t>72984</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>111815</t>
+          <t>114959</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>102683</t>
+          <t>103930</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>147100</t>
+          <t>146717</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>186300</t>
+          <t>188987</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>241056</t>
+          <t>242940</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>144024</t>
+          <t>145492</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>193888</t>
+          <t>193372</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>107531</t>
+          <t>110912</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>151605</t>
+          <t>154457</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>267691</t>
+          <t>266469</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>331396</t>
+          <t>334330</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>104165</t>
+          <t>100807</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>148653</t>
+          <t>145213</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64155</t>
+          <t>64065</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98090</t>
+          <t>98371</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>175605</t>
+          <t>177115</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>233650</t>
+          <t>232941</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>664450</t>
+          <t>661679</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>728939</t>
+          <t>730254</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>265647</t>
+          <t>266695</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>322421</t>
+          <t>322508</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>946196</t>
+          <t>944579</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1035651</t>
+          <t>1031565</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,6%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16802</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36459</t>
+          <t>36329</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>139844</t>
+          <t>136975</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>181961</t>
+          <t>182427</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>159017</t>
+          <t>162169</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>211289</t>
+          <t>210771</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>32393</t>
+          <t>31901</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>56750</t>
+          <t>57216</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>84833</t>
+          <t>85605</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>123386</t>
+          <t>124283</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>122404</t>
+          <t>124941</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>168848</t>
+          <t>170314</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52235</t>
+          <t>52481</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>83018</t>
+          <t>84502</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>102143</t>
+          <t>99857</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>141958</t>
+          <t>142357</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>160965</t>
+          <t>162650</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>213588</t>
+          <t>212573</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>45525</t>
+          <t>45773</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>74442</t>
+          <t>74759</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>34444</t>
+          <t>33884</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>62436</t>
+          <t>61052</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>86507</t>
+          <t>88642</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>126030</t>
+          <t>130987</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>296164</t>
+          <t>294682</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>338892</t>
+          <t>338171</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>300657</t>
+          <t>300147</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>357068</t>
+          <t>356635</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>612759</t>
+          <t>613230</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>684028</t>
+          <t>686890</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17201</t>
+          <t>16571</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>38181</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>171158</t>
+          <t>172265</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>226937</t>
+          <t>224081</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>195743</t>
+          <t>196525</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>251919</t>
+          <t>253165</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>15170</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>34986</t>
+          <t>33533</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>118019</t>
+          <t>117357</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>160967</t>
+          <t>160376</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>139215</t>
+          <t>141357</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>188686</t>
+          <t>187180</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>20569</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>41309</t>
+          <t>41022</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>203874</t>
+          <t>202174</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>257952</t>
+          <t>257662</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>231675</t>
+          <t>229662</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>289878</t>
+          <t>289404</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>41056</t>
+          <t>41152</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>67248</t>
+          <t>67255</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>87840</t>
+          <t>87253</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>126365</t>
+          <t>126831</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>137774</t>
+          <t>136479</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>184953</t>
+          <t>182982</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>118812</t>
+          <t>118948</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>151130</t>
+          <t>150624</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>402011</t>
+          <t>400296</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>470379</t>
+          <t>464378</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>531441</t>
+          <t>532837</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>603369</t>
+          <t>606330</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,19%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>236859</t>
+          <t>235464</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>301810</t>
+          <t>303105</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>665427</t>
+          <t>656654</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>763180</t>
+          <t>760481</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>914022</t>
+          <t>917951</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1044444</t>
+          <t>1036525</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>284933</t>
+          <t>285233</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>351716</t>
+          <t>355973</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>480342</t>
+          <t>476480</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>567785</t>
+          <t>562613</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>775101</t>
+          <t>785183</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>893852</t>
+          <t>896732</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>472016</t>
+          <t>472953</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>562142</t>
+          <t>559172</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>611662</t>
+          <t>609051</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>702792</t>
+          <t>707946</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1113554</t>
+          <t>1109769</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1234857</t>
+          <t>1231722</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>398654</t>
+          <t>403948</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>481484</t>
+          <t>481253</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>276435</t>
+          <t>275837</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>341355</t>
+          <t>345708</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>697008</t>
+          <t>694706</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>802770</t>
+          <t>800219</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1813482</t>
+          <t>1816826</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1935805</t>
+          <t>1935720</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1296487</t>
+          <t>1299596</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1415319</t>
+          <t>1417453</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3142576</t>
+          <t>3148897</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3319121</t>
+          <t>3311572</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57241</t>
+          <t>57364</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88689</t>
+          <t>89253</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94162</t>
+          <t>92951</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129142</t>
+          <t>128370</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>156514</t>
+          <t>159859</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>204316</t>
+          <t>206352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93322</t>
+          <t>93573</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130222</t>
+          <t>129153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94684</t>
+          <t>94813</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129489</t>
+          <t>127565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>198119</t>
+          <t>195600</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249868</t>
+          <t>249310</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60877</t>
+          <t>61838</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95358</t>
+          <t>93620</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49235</t>
+          <t>49224</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77126</t>
+          <t>76124</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118423</t>
+          <t>117838</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>161976</t>
+          <t>160349</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35067</t>
+          <t>35234</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60135</t>
+          <t>61973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17046</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36188</t>
+          <t>35987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58498</t>
+          <t>58061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89227</t>
+          <t>89609</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104112</t>
+          <t>104508</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>143494</t>
+          <t>141148</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25924</t>
+          <t>27044</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51789</t>
+          <t>51437</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136764</t>
+          <t>138837</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184309</t>
+          <t>188742</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42733</t>
+          <t>41818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70814</t>
+          <t>71084</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82198</t>
+          <t>82689</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117568</t>
+          <t>117772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131849</t>
+          <t>132745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>182370</t>
+          <t>179247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55346</t>
+          <t>54876</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85304</t>
+          <t>86158</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89365</t>
+          <t>91617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>126170</t>
+          <t>127358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156645</t>
+          <t>156323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202235</t>
+          <t>202008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51223</t>
+          <t>53222</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>83805</t>
+          <t>83649</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51964</t>
+          <t>52319</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81254</t>
+          <t>81180</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112211</t>
+          <t>113556</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>155874</t>
+          <t>154792</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39401</t>
+          <t>37893</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65594</t>
+          <t>65504</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19807</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41060</t>
+          <t>39183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63973</t>
+          <t>63789</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95612</t>
+          <t>98910</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112893</t>
+          <t>113860</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150533</t>
+          <t>152942</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54255</t>
+          <t>53737</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85520</t>
+          <t>85408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>176507</t>
+          <t>177116</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225630</t>
+          <t>225424</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>36946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65732</t>
+          <t>65124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20707</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42332</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64393</t>
+          <t>63500</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98809</t>
+          <t>97218</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88399</t>
+          <t>88240</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>124043</t>
+          <t>125741</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>34254</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55181</t>
+          <t>57239</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>129361</t>
+          <t>129472</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>172769</t>
+          <t>171664</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67706</t>
+          <t>68193</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102881</t>
+          <t>101807</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32991</t>
+          <t>32509</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>88375</t>
+          <t>88451</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>126089</t>
+          <t>125874</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44079</t>
+          <t>43631</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71407</t>
+          <t>71668</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23314</t>
+          <t>22287</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55534</t>
+          <t>54834</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88902</t>
+          <t>87202</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200286</t>
+          <t>199661</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246166</t>
+          <t>247065</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43109</t>
+          <t>44149</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68524</t>
+          <t>69645</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>253079</t>
+          <t>253369</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>305398</t>
+          <t>306322</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68880</t>
+          <t>69113</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105684</t>
+          <t>106712</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>151729</t>
+          <t>152518</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>199927</t>
+          <t>200154</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>231206</t>
+          <t>230590</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>289733</t>
+          <t>293062</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178962</t>
+          <t>177807</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>230343</t>
+          <t>233445</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>192929</t>
+          <t>193949</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>243752</t>
+          <t>241235</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>382572</t>
+          <t>383624</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>456510</t>
+          <t>457277</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>160398</t>
+          <t>160271</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>211400</t>
+          <t>210154</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126728</t>
+          <t>127854</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>170679</t>
+          <t>169721</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>302323</t>
+          <t>301068</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>368642</t>
+          <t>367005</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>130968</t>
+          <t>129942</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177684</t>
+          <t>177469</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62657</t>
+          <t>63767</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95858</t>
+          <t>97715</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>203635</t>
+          <t>207333</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>264664</t>
+          <t>263255</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>481144</t>
+          <t>479890</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>548230</t>
+          <t>550681</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>175578</t>
+          <t>178403</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>224146</t>
+          <t>228428</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8287,12 +8287,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>675599</t>
+          <t>675353</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>760072</t>
+          <t>759634</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28892</t>
+          <t>29169</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54436</t>
+          <t>54829</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>109654</t>
+          <t>108406</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>148912</t>
+          <t>149961</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>146241</t>
+          <t>143565</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>192001</t>
+          <t>194181</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8580,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>66887</t>
+          <t>64845</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>101948</t>
+          <t>102257</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>132340</t>
+          <t>132918</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>176401</t>
+          <t>177147</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>205833</t>
+          <t>209911</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>264693</t>
+          <t>266875</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>54630</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>87457</t>
+          <t>85256</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>117709</t>
+          <t>119407</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>160649</t>
+          <t>161026</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>184431</t>
+          <t>184275</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>239544</t>
+          <t>238907</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>43074</t>
+          <t>42121</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>72721</t>
+          <t>71312</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>50210</t>
+          <t>49617</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>81376</t>
+          <t>79710</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>98748</t>
+          <t>100707</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>143292</t>
+          <t>142394</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>344331</t>
+          <t>347559</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>395485</t>
+          <t>397218</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>226790</t>
+          <t>228009</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>276127</t>
+          <t>280433</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>585347</t>
+          <t>589533</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>657104</t>
+          <t>663813</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,92%</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>22927</t>
+          <t>23274</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>44308</t>
+          <t>44631</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>165124</t>
+          <t>168287</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>220029</t>
+          <t>220525</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>200053</t>
+          <t>198747</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>254051</t>
+          <t>256960</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -9262,12 +9262,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>59211</t>
+          <t>57861</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>88819</t>
+          <t>87346</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9297,12 +9297,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>251449</t>
+          <t>249934</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>308995</t>
+          <t>308888</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9332,12 +9332,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>317588</t>
+          <t>317656</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>383052</t>
+          <t>389289</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -9375,12 +9375,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>38752</t>
+          <t>39688</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>66033</t>
+          <t>64965</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9410,12 +9410,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>160400</t>
+          <t>158527</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>210433</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>208499</t>
+          <t>208300</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>265970</t>
+          <t>263955</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -9488,12 +9488,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>24896</t>
+          <t>25278</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>47485</t>
+          <t>48353</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>58082</t>
+          <t>58181</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>92830</t>
+          <t>94055</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>93005</t>
+          <t>90676</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>132903</t>
+          <t>131296</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -9601,12 +9601,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>77945</t>
+          <t>76170</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>108679</t>
+          <t>109704</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9636,12 +9636,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>313330</t>
+          <t>313361</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>378561</t>
+          <t>376521</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>404776</t>
+          <t>402995</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>470487</t>
+          <t>472700</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,72%</t>
         </is>
       </c>
     </row>
@@ -9831,12 +9831,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>300926</t>
+          <t>300228</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>371789</t>
+          <t>373843</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9846,12 +9846,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9866,12 +9866,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>687292</t>
+          <t>692620</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>784824</t>
+          <t>789039</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1008889</t>
+          <t>1012333</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1138492</t>
+          <t>1138877</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -9944,12 +9944,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>602224</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>696258</t>
+          <t>695689</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9959,12 +9959,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>864947</t>
+          <t>857672</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>969984</t>
+          <t>964694</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1491724</t>
+          <t>1482437</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1633060</t>
+          <t>1627412</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>492310</t>
+          <t>491891</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>578191</t>
+          <t>575998</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10072,12 +10072,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>578426</t>
+          <t>579171</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>668481</t>
+          <t>672081</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1096499</t>
+          <t>1097476</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1222439</t>
+          <t>1219948</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -10170,12 +10170,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>360421</t>
+          <t>364932</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>438392</t>
+          <t>437147</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>252664</t>
+          <t>253848</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>317950</t>
+          <t>317574</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>630118</t>
+          <t>638451</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>737876</t>
+          <t>735301</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -10283,12 +10283,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1400057</t>
+          <t>1399185</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1513282</t>
+          <t>1515952</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>902875</t>
+          <t>908669</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1015806</t>
+          <t>1012530</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2336547</t>
+          <t>2334526</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2501981</t>
+          <t>2492001</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
